--- a/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
+++ b/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28715"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-us\InputData\web-app\OCCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\web-app\OCCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{6B6FEF58-08A4-48D5-A6A7-14155C535D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEC4F9A2-C634-4475-8D19-9008F6E7DE94}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="23955" windowHeight="11325"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -17,16 +18,44 @@
     <sheet name="OCCF-DpMOCU" sheetId="4" r:id="rId3"/>
     <sheet name="OCCF-DpSOCU" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+  <si>
+    <t>OCCF Dollars per Large Output Currency Unit</t>
+  </si>
+  <si>
+    <t>OCCF Dollars per Medium Output Currency Unit</t>
+  </si>
+  <si>
+    <t>OCCF Dollars per Small Output Currency Unit</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>See cpi.xlsx</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -48,74 +77,68 @@
     <t>web application interface do not get too large.</t>
   </si>
   <si>
+    <t>For the U.S. model:</t>
+  </si>
+  <si>
+    <t>Large Output Currency Unit</t>
+  </si>
+  <si>
+    <t>billion 2023 Mexican Pesos (MXN)</t>
+  </si>
+  <si>
+    <t>Medium Output Currency Unit</t>
+  </si>
+  <si>
+    <t>million 2023 Mexican Pesos (MXN)</t>
+  </si>
+  <si>
+    <t>Small Output Currency Unit</t>
+  </si>
+  <si>
+    <t>2023 Mexican Pesos (MXN)</t>
+  </si>
+  <si>
+    <t>2023 MXN per 2012 USD</t>
+  </si>
+  <si>
+    <t>2023 MXN per 2023 USD</t>
+  </si>
+  <si>
+    <t>2023 USD per 2012 USD</t>
+  </si>
+  <si>
+    <t>Recall, this variable is "dollars per large/medium/small currency output unit"</t>
+  </si>
+  <si>
+    <t>which in this case is "2012 dollars per 2023 dollar."</t>
+  </si>
+  <si>
+    <t>2012 dollars are worth more than 2020 dollars, so we need a</t>
+  </si>
+  <si>
+    <t>value less than 1 in this variable.</t>
+  </si>
+  <si>
+    <t>This is why we multiply, not divide, by the conversion</t>
+  </si>
+  <si>
+    <t>factor above.</t>
+  </si>
+  <si>
+    <t>One Large Output Currency Unit</t>
+  </si>
+  <si>
     <t>Dollars</t>
   </si>
   <si>
-    <t>One Large Output Currency Unit</t>
-  </si>
-  <si>
-    <t>For the U.S. model:</t>
-  </si>
-  <si>
-    <t>Large Output Currency Unit</t>
-  </si>
-  <si>
-    <t>Small Output Currency Unit</t>
-  </si>
-  <si>
     <t>One Small Output Currency Unit</t>
   </si>
-  <si>
-    <t>OCCF Dollars per Large Output Currency Unit</t>
-  </si>
-  <si>
-    <t>OCCF Dollars per Small Output Currency Unit</t>
-  </si>
-  <si>
-    <t>2018 dollars</t>
-  </si>
-  <si>
-    <t>See cpi.xlsx</t>
-  </si>
-  <si>
-    <t>2012 dollars are worth more than 2018 dollars, so we need a</t>
-  </si>
-  <si>
-    <t>value less than 1 in this variable.</t>
-  </si>
-  <si>
-    <t>This is why we multiply, not divide, by the conversion</t>
-  </si>
-  <si>
-    <t>factor above.</t>
-  </si>
-  <si>
-    <t>Medium Output Currency Unit</t>
-  </si>
-  <si>
-    <t>OCCF Dollars per Medium Output Currency Unit</t>
-  </si>
-  <si>
-    <t>Recall, this variable is "dollars per large/medium/small currency output unit"</t>
-  </si>
-  <si>
-    <t>2019 dollars per 2012 dollar</t>
-  </si>
-  <si>
-    <t>which in this case is "2012 dollars per 2019 dollar."</t>
-  </si>
-  <si>
-    <t>million 2019 dollars</t>
-  </si>
-  <si>
-    <t>billion 2019 dollars</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,17 +181,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -188,9 +209,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -228,9 +249,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -265,7 +286,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -300,7 +321,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -473,145 +494,162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="26.265625" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+    <row r="20" spans="1:2">
+      <c r="A20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <f>1/(1/A29/A28)</f>
+        <v>4.2542803263516484E-2</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15">
+      <c r="A28">
+        <v>5.6460000000000003E-2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>0.75350342301658668</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="B32" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="6"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="6"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26">
-        <v>0.89805481563188172</v>
-      </c>
-      <c r="B26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B33" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -621,28 +659,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="31.265625" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
+      <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3">
-        <f>10^9*About!$A$26</f>
-        <v>898054815.63188171</v>
+        <v>29</v>
+      </c>
+      <c r="B2" s="2">
+        <f>10^9*About!$A$29</f>
+        <v>753503423.01658666</v>
       </c>
     </row>
   </sheetData>
@@ -651,28 +689,28 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="31.265625" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B1" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
+      <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="8">
-        <f>10^6*About!$A$26</f>
-        <v>898054.81563188171</v>
+        <v>29</v>
+      </c>
+      <c r="B2" s="6">
+        <f>10^6*About!$A$29</f>
+        <v>753503.42301658669</v>
       </c>
     </row>
   </sheetData>
@@ -681,31 +719,202 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="31.265625" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B1" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
+      <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="7">
-        <f>1*About!A26</f>
-        <v>0.89805481563188172</v>
+        <v>29</v>
+      </c>
+      <c r="B2">
+        <f>1*About!A29</f>
+        <v>0.75350342301658668</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{344CD8FC-E2A0-4EE7-AFF9-D02002E55732}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA9BC424-9974-4873-AEBE-9FBC926B8FEA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17CFF595-95A3-4F62-9F72-80600493741F}"/>
 </file>
--- a/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
+++ b/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28715"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\web-app\OCCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\web-app\OCCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{6B6FEF58-08A4-48D5-A6A7-14155C535D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEC4F9A2-C634-4475-8D19-9008F6E7DE94}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA2F14E-082D-4A6C-8CE3-BEBFA3E084DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="48015" yWindow="2685" windowWidth="18480" windowHeight="12900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -83,21 +83,12 @@
     <t>Large Output Currency Unit</t>
   </si>
   <si>
-    <t>billion 2023 Mexican Pesos (MXN)</t>
-  </si>
-  <si>
     <t>Medium Output Currency Unit</t>
   </si>
   <si>
-    <t>million 2023 Mexican Pesos (MXN)</t>
-  </si>
-  <si>
     <t>Small Output Currency Unit</t>
   </si>
   <si>
-    <t>2023 Mexican Pesos (MXN)</t>
-  </si>
-  <si>
     <t>2023 MXN per 2012 USD</t>
   </si>
   <si>
@@ -132,13 +123,22 @@
   </si>
   <si>
     <t>One Small Output Currency Unit</t>
+  </si>
+  <si>
+    <t>2023 Mexican Pesos (MXN$)</t>
+  </si>
+  <si>
+    <t>million 2023 Mexican Pesos (MXN$)</t>
+  </si>
+  <si>
+    <t>billion 2023 Mexican Pesos (MXN$)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -496,27 +496,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -524,132 +524,132 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="5"/>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="4" t="s">
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="5"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="B23" s="5"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>1/(1/A29/A28)</f>
         <v>4.2542803263516484E-2</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>5.6460000000000003E-2</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.75350342301658668</v>
       </c>
       <c r="B29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="B31" t="s">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="B32" t="s">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
-      <c r="B33" t="s">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -664,19 +664,19 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B1" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2">
         <f>10^9*About!$A$29</f>
@@ -694,19 +694,19 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B1" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2" s="6">
         <f>10^6*About!$A$29</f>
@@ -724,19 +724,19 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B1" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <f>1*About!A29</f>
@@ -749,21 +749,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -907,14 +892,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{344CD8FC-E2A0-4EE7-AFF9-D02002E55732}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17CFF595-95A3-4F62-9F72-80600493741F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA9BC424-9974-4873-AEBE-9FBC926B8FEA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA9BC424-9974-4873-AEBE-9FBC926B8FEA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17CFF595-95A3-4F62-9F72-80600493741F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{344CD8FC-E2A0-4EE7-AFF9-D02002E55732}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>